--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488057_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488057_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>D. GUAITA MACHADO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4191</v>
+        <v>5.8863</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4191</v>
+        <v>3.9163</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.9701</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3797</v>
+        <v>3.5773</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0418</v>
+        <v>-0.8288</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4215</v>
+        <v>4.4061</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6267</v>
+        <v>4.7534</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0202</v>
+        <v>0.3701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6066</v>
+        <v>4.3833</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7529</v>
+        <v>-1.1761</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.062</v>
+        <v>-1.1989</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.0228</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9911</v>
+        <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1673</v>
+        <v>0.1771</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3782</v>
+        <v>-0.4495</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7891</v>
+        <v>0.6266</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8811</v>
+        <v>0.7444</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4142</v>
+        <v>0.6036</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5331</v>
+        <v>0.1408</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GUAITA MACHADO</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2969</v>
+        <v>4.9346</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2427</v>
+        <v>3.2154</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0543</v>
+        <v>1.7192</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5773</v>
+        <v>1.3797</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8288</v>
+        <v>-0.0418</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4061</v>
+        <v>1.4215</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7534</v>
+        <v>0.6267</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3701</v>
+        <v>0.0202</v>
       </c>
       <c r="L3" t="n">
-        <v>4.3833</v>
+        <v>0.6066</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1761</v>
+        <v>0.7529</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1989</v>
+        <v>-0.062</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0228</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4123</v>
+        <v>0.6827</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1232</v>
+        <v>0.1744</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7109</v>
+        <v>0.5083</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7444</v>
+        <v>1.8811</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6036</v>
+        <v>2.4142</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1408</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>A. MARTIN ALCAINE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.9333</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.85</v>
+        <v>0.8984</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7225</v>
+        <v>1.0349</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6766</v>
+        <v>-1.5057</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3686</v>
+        <v>-1.1423</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3079</v>
+        <v>-0.3634</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7193000000000001</v>
+        <v>-1.003</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5586</v>
+        <v>-0.215</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1607</v>
+        <v>-0.788</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0428</v>
+        <v>-0.5027</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.19</v>
+        <v>-0.9272</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1472</v>
+        <v>0.4246</v>
       </c>
       <c r="P4" t="n">
+        <v>1.3876</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.9733</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5131</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0696</v>
+        <v>0.4783</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5827</v>
+        <v>0.366</v>
       </c>
       <c r="V4" t="n">
-        <v>0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4737</v>
+        <v>2.4142</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7997</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MARTIN ALCAINE</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5058</v>
+        <v>1.6318</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0605</v>
+        <v>1.1491</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4453</v>
+        <v>0.4828</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5057</v>
+        <v>-1.3611</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1423</v>
+        <v>-1.3938</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3634</v>
+        <v>0.0327</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.003</v>
+        <v>0.9522</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.215</v>
+        <v>-0.2687</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.788</v>
+        <v>1.2209</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5027</v>
+        <v>-2.3133</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9272</v>
+        <v>-1.1251</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4246</v>
+        <v>-1.1882</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3876</v>
+        <v>2.3787</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3787</v>
+        <v>3.3698</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5832000000000001</v>
+        <v>-0.5929</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3596</v>
+        <v>-0.0191</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2236</v>
+        <v>-0.5737</v>
       </c>
       <c r="V5" t="n">
         <v>1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4142</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4498</v>
+        <v>0.4337</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1075</v>
+        <v>-0.9518</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3424</v>
+        <v>1.3855</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3611</v>
+        <v>0.6766</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3938</v>
+        <v>0.3686</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0327</v>
+        <v>0.3079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9522</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2687</v>
+        <v>0.5586</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2209</v>
+        <v>0.1607</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3133</v>
+        <v>-0.0428</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1251</v>
+        <v>-0.19</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1882</v>
+        <v>0.1472</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3787</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3698</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7749</v>
+        <v>0.0743</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0608</v>
+        <v>-0.1715</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7141</v>
+        <v>0.2458</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>0.674</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2999</v>
+        <v>0.1181</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7103</v>
+        <v>-0.4047</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4105</v>
+        <v>0.5228</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0458</v>
@@ -1000,13 +1000,13 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1857</v>
+        <v>0.2322</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0514</v>
+        <v>0.2542</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1344</v>
+        <v>-0.0221</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2666</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6053</v>
+        <v>-2.9952</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.44</v>
+        <v>-3.5771</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8347</v>
+        <v>0.582</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2034</v>
@@ -1078,13 +1078,13 @@
         <v>2.5769</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2433</v>
+        <v>0.8535</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2211</v>
+        <v>1.084</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0222</v>
+        <v>-0.2305</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.499</v>
+        <v>-3.1164</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.955</v>
+        <v>-2.6846</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5441</v>
+        <v>-0.4318</v>
       </c>
       <c r="G9" t="n">
         <v>0.1638</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3194</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7402</v>
+        <v>1.0106</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4209</v>
+        <v>-0.3085</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6186</v>
+        <v>-3.4833</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.334</v>
+        <v>-4.3111</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7154</v>
+        <v>0.8278</v>
       </c>
       <c r="G10" t="n">
         <v>-5.7376</v>
@@ -1234,13 +1234,13 @@
         <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7137</v>
+        <v>0.8489</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9435</v>
+        <v>0.9665</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2299</v>
+        <v>-0.1176</v>
       </c>
       <c r="V10" t="n">
         <v>1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7801</v>
+        <v>-4.6658</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6249</v>
+        <v>-4.3983</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1552</v>
+        <v>-0.2675</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3839</v>
@@ -1312,13 +1312,13 @@
         <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2841</v>
+        <v>-0.1698</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>0.1057</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1631</v>
+        <v>-0.2754</v>
       </c>
       <c r="V11" t="n">
         <v>0.2666</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.258799999999999</v>
+        <v>0.6771000000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.0844</v>
+        <v>-7.1484</v>
       </c>
       <c r="F12" t="n">
-        <v>7.825799999999999</v>
+        <v>7.825800000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.440100000000001</v>
+        <v>-6.440099999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.099699999999999</v>
+        <v>-9.0997</v>
       </c>
       <c r="I12" t="n">
         <v>2.6596</v>
@@ -1381,7 +1381,7 @@
         <v>-1.1586</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.982200000000001</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q12" t="n">
         <v>-20.8134</v>
@@ -1390,13 +1390,13 @@
         <v>18.8312</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7166</v>
+        <v>3.6524</v>
       </c>
       <c r="T12" t="n">
-        <v>2.497399999999999</v>
+        <v>3.4336</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2189000000000001</v>
+        <v>0.2189</v>
       </c>
       <c r="V12" t="n">
         <v>5.447100000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.566</v>
+        <v>7.5064</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7567</v>
+        <v>6.6735</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8094</v>
+        <v>0.8329</v>
       </c>
       <c r="G13" t="n">
         <v>4.2776</v>
@@ -1468,13 +1468,13 @@
         <v>3.568</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7357</v>
+        <v>0.2046</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9139</v>
+        <v>0.0029</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1782</v>
+        <v>0.2017</v>
       </c>
       <c r="V13" t="n">
         <v>1.6366</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6858</v>
+        <v>2.3882</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5837</v>
+        <v>2.9538</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.898</v>
+        <v>-0.5656</v>
       </c>
       <c r="G14" t="n">
         <v>2.568</v>
@@ -1546,13 +1546,13 @@
         <v>2.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0033</v>
+        <v>0.7058</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7937</v>
+        <v>1.1638</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7904</v>
+        <v>-0.4581</v>
       </c>
       <c r="V14" t="n">
         <v>-3.066</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6652</v>
+        <v>1.6957</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.5232</v>
+        <v>-2.7082</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1884</v>
+        <v>4.4039</v>
       </c>
       <c r="G15" t="n">
         <v>0.5537</v>
@@ -1624,13 +1624,13 @@
         <v>3.1716</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3554</v>
+        <v>-0.3249</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2369</v>
+        <v>-0.422</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1185</v>
+        <v>0.097</v>
       </c>
       <c r="V15" t="n">
         <v>0.674</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUNOZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3315</v>
+        <v>-0.6891</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8229</v>
+        <v>-2.8936</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1544</v>
+        <v>2.2045</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1504</v>
+        <v>-0.5322</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7815</v>
+        <v>0.281</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9319</v>
+        <v>-0.8131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8204</v>
+        <v>-1.1703</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6999</v>
+        <v>-0.6117</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>-0.5586</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9708</v>
+        <v>0.6381</v>
       </c>
       <c r="N18" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.8927</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0524</v>
+        <v>-0.2545</v>
       </c>
       <c r="P18" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.5858</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.1893</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.7751</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.5548</v>
+        <v>-0.7516</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9253</v>
+        <v>-0.7322</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3705</v>
+        <v>-0.0194</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3217</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8327</v>
+        <v>-0.8621</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1229</v>
+        <v>-0.4285</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7098</v>
+        <v>-0.4336</v>
       </c>
       <c r="G19" t="n">
         <v>0.9107</v>
@@ -1936,13 +1936,13 @@
         <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6662</v>
+        <v>-0.6956</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0552</v>
+        <v>-0.2505</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7214</v>
+        <v>-0.4451</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4737</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>J. LOPEZ MUNOZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2814</v>
+        <v>-0.9394</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0974</v>
+        <v>-0.0939</v>
       </c>
       <c r="F20" t="n">
-        <v>1.816</v>
+        <v>-0.8455</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5322</v>
+        <v>-0.1504</v>
       </c>
       <c r="H20" t="n">
-        <v>0.281</v>
+        <v>0.7815</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8131</v>
+        <v>-0.9319</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1703</v>
+        <v>0.8204</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6117</v>
+        <v>0.6999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5586</v>
+        <v>0.1205</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6381</v>
+        <v>-0.9708</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8927</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2545</v>
+        <v>-1.0524</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>2.7751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3439</v>
+        <v>-0.0532</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4079</v>
+        <v>-0.0616</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.3217</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.5882</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5887</v>
+        <v>-1.1531</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5272</v>
+        <v>-0.1197</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0614</v>
+        <v>-1.0334</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3981</v>
@@ -2092,13 +2092,13 @@
         <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3888</v>
+        <v>0.0468</v>
       </c>
       <c r="T21" t="n">
-        <v>0.011</v>
+        <v>0.4185</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3998</v>
+        <v>-0.3717</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9443</v>
+        <v>-1.7216</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4858</v>
+        <v>-3.2821</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5416</v>
+        <v>1.5605</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0496</v>
@@ -2170,13 +2170,13 @@
         <v>1.3876</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1523</v>
+        <v>-0.9297</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.7322</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2164</v>
+        <v>-0.1974</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9405</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6254</v>
+        <v>-2.6648</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0155</v>
+        <v>-5.0148</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3902</v>
+        <v>2.35</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2534</v>
+        <v>-2.1985</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8854</v>
+        <v>-1.657</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.632</v>
+        <v>-0.5415</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2295</v>
+        <v>-2.7707</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1414</v>
+        <v>-1.5329</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0881</v>
+        <v>-1.2377</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9761</v>
+        <v>0.5722</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.256</v>
+        <v>-0.1241</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7201</v>
+        <v>0.6962</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.352</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-8.1272</v>
+        <v>-2.1805</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7751</v>
+        <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5215</v>
+        <v>-0.5589</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7564</v>
+        <v>-0.3303</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7651</v>
+        <v>-0.2286</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0483</v>
+        <v>0.0925</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1258</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
         <v>-0.174</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2597</v>
+        <v>-3.1484</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4223</v>
+        <v>-4.1174</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1626</v>
+        <v>0.969</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1985</v>
+        <v>1.2534</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.657</v>
+        <v>2.8854</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5415</v>
+        <v>-1.632</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7707</v>
+        <v>3.2295</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5329</v>
+        <v>3.1414</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2377</v>
+        <v>0.0881</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5722</v>
+        <v>-1.9761</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1241</v>
+        <v>-0.256</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6962</v>
+        <v>-1.7201</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-5.352</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1805</v>
+        <v>-8.1272</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1805</v>
+        <v>2.7751</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1538</v>
+        <v>0.9984</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7377</v>
+        <v>0.6545</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4161</v>
+        <v>0.344</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0925</v>
+        <v>-0.0483</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0.1258</v>
       </c>
       <c r="X24" t="n">
         <v>-0.174</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2587000000000006</v>
+        <v>1.617200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.8256</v>
+        <v>-7.8255</v>
       </c>
       <c r="F25" t="n">
-        <v>8.0846</v>
+        <v>9.442699999999999</v>
       </c>
       <c r="G25" t="n">
         <v>6.44</v>
@@ -2404,13 +2404,13 @@
         <v>20.8135</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.7165</v>
+        <v>-1.3583</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2189000000000003</v>
+        <v>-0.2191</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.4977</v>
+        <v>-1.1392</v>
       </c>
       <c r="V25" t="n">
         <v>-5.4471</v>
